--- a/data/trans_orig/IP13_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Provincia-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (Tasa respuesta: 99,9%)</t>
+          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,79 +700,127 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3420</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3420</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7253</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,67%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1831</v>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>5251</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2141</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10075</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>69862</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>77535</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>147397</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>73282</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>69862</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>66029</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>79366</v>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>77535</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>152648</v>
+          <t>73354</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>79366</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>147397</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>142573</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>150507</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Cadiz</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>5139</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73282</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>73282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>73282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>8357</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>79366</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>13497</v>
+          <t>79366</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>79366</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>152648</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>152648</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>152648</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>121700</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>119239</v>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>278</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>240938</v>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7504</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>7729</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>14040</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>126839</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>127596</v>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>254435</v>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>10313</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>5767</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Cordoba</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>4112</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121700</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>116244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>125014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>3802</v>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>91,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>144</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>119239</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>7914</v>
+          <t>112611</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>123154</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>240938</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>232031</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>246290</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>54156</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126839</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>126839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>126839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>63361</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>127596</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>117517</v>
+          <t>127596</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>127596</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>254435</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>254435</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>254435</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>58268</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>67163</v>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>125431</v>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>5441</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>10452</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>2445</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>2212</v>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>4656</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5786</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>67698</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54156</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>50007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>56855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>75922</v>
+          <t>92,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>143622</v>
+          <t>58534</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>65890</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>117517</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>111872</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>121135</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>70143</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58268</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>78134</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67163</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>148278</v>
+          <t>67163</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>67163</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,6 +2040,36 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>125431</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>125431</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>125431</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1530,75 +2078,117 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>2530</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>3569</v>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>6100</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7366</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>8805</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1606,70 +2196,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>31983</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>37150</v>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>968</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>69132</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6403</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1677,216 +2309,342 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>34513</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>67698</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>63413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>40719</v>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75922</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>75232</v>
+          <t>69715</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>78134</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>143622</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>137283</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>146795</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Jaen</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>3677</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>70143</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>3627</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>7303</v>
+          <t>78134</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>78134</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>148278</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>148278</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>148278</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>42490</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>52559</v>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>95050</v>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>9099</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -1894,145 +2652,225 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>46167</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>56186</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>102353</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>11412</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>31983</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>28696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>16113</v>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>83,15%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>37150</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>27525</v>
+          <t>32917</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>39289</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>69132</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>64925</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>72135</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>91,89%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -2040,216 +2878,342 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>113096</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>34513</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>139175</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>40719</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>316</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>252272</v>
+          <t>40719</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>40719</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>124508</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1761</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>155288</v>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>353</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>279797</v>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6927</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>5029</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2414</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>9775</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>4701</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>8907</v>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>358</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>13608</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2274</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -2260,67 +3224,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>126918</v>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>42490</t>
+        </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>147888</v>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>83,47%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>52559</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>377</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>274806</v>
+          <t>48808</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>54832</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>93,55%</t>
+        </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>95050</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>89908</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>98231</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>92,86%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>87,84%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2331,20 +3337,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>131619</v>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>46167</t>
+        </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>46167</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>46167</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2352,32 +3362,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>156795</v>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>399</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>288414</v>
+          <t>56186</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>56186</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -2390,6 +3408,36 @@
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>102353</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>102353</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>102353</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2398,75 +3446,117 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>37437</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6331</t>
+        </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>48417</v>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>85854</v>
+          <t>7938</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>20529</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>19867</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>12935</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>28869</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -2474,70 +3564,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>884</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>627903</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5082</t>
+        </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>910</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>712831</v>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>1794</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>1340734</v>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>6911</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>7658</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>13994</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2545,75 +3677,1142 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>942</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>665340</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>113096</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>106735</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>117417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>761248</v>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>85,73%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>94,31%</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>139175</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>1918</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>1426588</v>
+          <t>131092</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>144797</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>252272</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>241862</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>260502</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>124508</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>124508</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>124508</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>155288</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>155288</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>155288</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>279797</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>279797</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>279797</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4258</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>8132</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>8039</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>4181</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>14363</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>12297</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>7614</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>19216</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>4327</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>126918</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>122808</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>129471</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>147888</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>141555</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>152027</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>274806</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>267772</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>279793</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>131619</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>131619</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>131619</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>156795</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>156795</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>156795</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>288414</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>288414</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>288414</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>19011</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>36467</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>26271</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>47471</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>63411</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>51509</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>77482</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>5914</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>16840</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>6848</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>19006</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>14731</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>31003</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>627903</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>617047</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>637527</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>712831</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>701590</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>724706</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1340734</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>1324469</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>1355278</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>1426588</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>1426588</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>1426588</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -2621,19 +4820,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP13_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66029</t>
+          <t>65515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>72019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73354</t>
+          <t>73488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>142573</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>150507</t>
+          <t>150724</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125014</t>
+          <t>124974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112611</t>
+          <t>112489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123154</t>
+          <t>122950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232031</t>
+          <t>234030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246290</t>
+          <t>246514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>49480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56855</t>
+          <t>56682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>57920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65890</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111872</t>
+          <t>111299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>121174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63413</t>
+          <t>63636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69554</t>
+          <t>69559</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69715</t>
+          <t>70534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137283</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>146795</t>
+          <t>146670</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32917</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64925</t>
+          <t>64359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72135</t>
+          <t>72062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38772</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44571</t>
+          <t>44523</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89908</t>
+          <t>90173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98231</t>
+          <t>98568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28869</t>
+          <t>27822</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>796</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106735</t>
+          <t>106738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>117417</t>
+          <t>117881</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>131092</t>
+          <t>130493</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>144797</t>
+          <t>144845</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>241862</t>
+          <t>242378</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>260502</t>
+          <t>260175</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>122808</t>
+          <t>122743</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>129471</t>
+          <t>129357</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>141555</t>
+          <t>141690</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>152027</t>
+          <t>151952</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>267406</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>279793</t>
+          <t>279841</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77482</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,47 +4506,47 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>617047</t>
+          <t>618104</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>637527</t>
+          <t>637340</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>701590</t>
+          <t>699766</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1324469</t>
+          <t>1324144</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1355278</t>
+          <t>1355038</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3420</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7767</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62616</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>58466</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69862</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>72019</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>89,4%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77535</t>
+          <t>53413</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73488</t>
+          <t>49890</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>147397</t>
+          <t>116029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>142186</t>
+          <t>111396</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>150724</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10173</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>4952</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11865</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108363</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>102379</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>111989</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>121700</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>115631</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>124974</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>119239</t>
+          <t>95406</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112489</t>
+          <t>90087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122950</t>
+          <t>98551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>240938</t>
+          <t>203770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234030</t>
+          <t>196462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246514</t>
+          <t>209057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2240</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7141</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>910</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56227</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52640</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58360</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>54156</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49480</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56682</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63361</t>
+          <t>52648</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65871</t>
+          <t>55208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>117517</t>
+          <t>108876</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111299</t>
+          <t>103772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121174</t>
+          <t>112181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5027</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7207</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5903</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>979</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>987</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>69997</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>65240</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>67698</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63636</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>69559</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>75922</t>
+          <t>68218</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70534</t>
+          <t>62528</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>143622</t>
+          <t>138214</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137529</t>
+          <t>131680</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>146670</t>
+          <t>141393</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2530</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5565</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>35885</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>32126</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>37946</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>81,17%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>31983</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>28948</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>33519</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37150</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>29893</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39584</t>
+          <t>34800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>69132</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64359</t>
+          <t>64273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72062</t>
+          <t>71739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,72 +3000,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2798</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1761</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -3113,72 +3113,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>45896</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>42207</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>47600</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>42490</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>38772</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>44523</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>83,98%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>52559</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>38310</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54919</t>
+          <t>44357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>95050</t>
+          <t>87884</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90173</t>
+          <t>83639</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98568</t>
+          <t>91311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>12882</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>7746</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>19739</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>6331</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2939</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>11771</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27323</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2660</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7977</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>5082</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>2203</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>10168</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>125289</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>117517</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>130926</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>88,96%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>92,97%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>113096</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>106738</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>85,73%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>139175</t>
+          <t>110962</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>130493</t>
+          <t>104010</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>144845</t>
+          <t>115363</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>252272</t>
+          <t>236252</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>242378</t>
+          <t>227082</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>260175</t>
+          <t>243891</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3912,74 +3912,74 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>8085</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>13937</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>4258</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1911</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>8295</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4055,77 +4055,77 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4138,72 +4138,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>150386</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>144515</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>154878</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>94,33%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>90,65%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>126918</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>122743</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>129357</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>147888</t>
+          <t>136407</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>141690</t>
+          <t>132739</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>151952</t>
+          <t>138739</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>274806</t>
+          <t>286793</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>267406</t>
+          <t>279905</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>279841</t>
+          <t>292044</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -4251,57 +4251,57 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4368,72 +4368,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>34234</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>44933</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>18874</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>35042</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77859</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4594,72 +4594,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>654660</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>641976</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>664532</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>884</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>627903</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>618104</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>637340</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>712831</t>
+          <t>592056</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>699766</t>
+          <t>581075</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>723830</t>
+          <t>600792</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1340734</t>
+          <t>1246716</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1324144</t>
+          <t>1229241</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1355038</t>
+          <t>1260932</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -4707,57 +4707,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
